--- a/ValueSet-i2x-pneumo-diagnostic.xlsx
+++ b/ValueSet-i2x-pneumo-diagnostic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -99,6 +99,108 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>233703007</t>
+  </si>
+  <si>
+    <t>pneumopathie interstitielle diffuse</t>
+  </si>
+  <si>
+    <t>51615001</t>
+  </si>
+  <si>
+    <t>fibrose pulmonaire</t>
+  </si>
+  <si>
+    <t>708030004</t>
+  </si>
+  <si>
+    <t>emphysème pulmonaire concomitant à une fibrose pulmonaire</t>
+  </si>
+  <si>
+    <t>1172606002</t>
+  </si>
+  <si>
+    <t>fibroélastose pleuroparenchymateuse idiopathique</t>
+  </si>
+  <si>
+    <t>700249006</t>
+  </si>
+  <si>
+    <t>pneumonie interstitielle idiopathique</t>
+  </si>
+  <si>
+    <t>782964007</t>
+  </si>
+  <si>
+    <t>maladie génétique</t>
+  </si>
+  <si>
+    <t>105969002</t>
+  </si>
+  <si>
+    <t>affection d'un tissu conjonctif</t>
+  </si>
+  <si>
+    <t>870573008</t>
+  </si>
+  <si>
+    <t>pneumonie interstitielle avec des caractéristiques auto-immunes</t>
+  </si>
+  <si>
+    <t>37471005</t>
+  </si>
+  <si>
+    <t>Hypersensitivity pneumonitis</t>
+  </si>
+  <si>
+    <t>40122008</t>
+  </si>
+  <si>
+    <t>pneumoconiose</t>
+  </si>
+  <si>
+    <t>31541009</t>
+  </si>
+  <si>
+    <t>sarcoïdose</t>
+  </si>
+  <si>
+    <t>31996006</t>
+  </si>
+  <si>
+    <t>vascularite</t>
+  </si>
+  <si>
+    <t>87119009</t>
+  </si>
+  <si>
+    <t>poumon kystique congénital</t>
+  </si>
+  <si>
+    <t>70995007</t>
+  </si>
+  <si>
+    <t>hypertension pulmonaire</t>
+  </si>
+  <si>
+    <t>11399002</t>
+  </si>
+  <si>
+    <t>hypertension artérielle pulmonaire</t>
+  </si>
+  <si>
+    <t>84114007</t>
+  </si>
+  <si>
+    <t>insuffisance cardiaque</t>
+  </si>
+  <si>
+    <t>76267008</t>
+  </si>
+  <si>
+    <t>valvulopathie pulmonaire</t>
+  </si>
+  <si>
     <t>195967001</t>
   </si>
   <si>
@@ -109,12 +211,6 @@
   </si>
   <si>
     <t>bronchite chronique</t>
-  </si>
-  <si>
-    <t>102361000119104</t>
-  </si>
-  <si>
-    <t>pneumonie chronique</t>
   </si>
   <si>
     <t>2561000112106</t>
@@ -396,7 +492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -453,18 +549,146 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-i2x-pneumo-diagnostic.xlsx
+++ b/ValueSet-i2x-pneumo-diagnostic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
   <si>
     <t>Property</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Jeu de diagnostic principal maladie respiratoire</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -79,6 +76,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Valueset for principal diagnosis in the scope of he 'Vers Un Souffle Nouveau' project</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -405,62 +405,60 @@
       <c r="A5" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>13</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>15</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>17</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -504,7 +502,7 @@
         <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
@@ -677,10 +675,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">

--- a/ValueSet-i2x-pneumo-diagnostic.xlsx
+++ b/ValueSet-i2x-pneumo-diagnostic.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-pneumo-diagnostic.xlsx
+++ b/ValueSet-i2x-pneumo-diagnostic.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -129,18 +129,6 @@
     <t>pneumonie interstitielle idiopathique</t>
   </si>
   <si>
-    <t>782964007</t>
-  </si>
-  <si>
-    <t>maladie génétique</t>
-  </si>
-  <si>
-    <t>105969002</t>
-  </si>
-  <si>
-    <t>affection d'un tissu conjonctif</t>
-  </si>
-  <si>
     <t>870573008</t>
   </si>
   <si>
@@ -159,10 +147,10 @@
     <t>pneumoconiose</t>
   </si>
   <si>
-    <t>31541009</t>
-  </si>
-  <si>
-    <t>sarcoïdose</t>
+    <t>24369008</t>
+  </si>
+  <si>
+    <t>sarcoïdose pulmonaire</t>
   </si>
   <si>
     <t>31996006</t>
@@ -187,12 +175,6 @@
   </si>
   <si>
     <t>hypertension artérielle pulmonaire</t>
-  </si>
-  <si>
-    <t>84114007</t>
-  </si>
-  <si>
-    <t>insuffisance cardiaque</t>
   </si>
   <si>
     <t>76267008</t>
@@ -490,7 +472,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -651,42 +633,18 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
